--- a/motor_renewals_tracking.xlsx
+++ b/motor_renewals_tracking.xlsx
@@ -1826,9 +1826,21 @@
       <c r="E37" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No Answer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Whatsapp message sent</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -2078,9 +2090,21 @@
       <c r="E45" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Reminded</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
     </row>
@@ -2282,9 +2306,21 @@
       <c r="E51" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Reminded</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -4110,8 +4146,16 @@
       <c r="E103" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -4483,14 +4527,10 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">He will come </t>
-        </is>
-      </c>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
     </row>
@@ -23324,9 +23364,21 @@
       <c r="E706" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F706" t="inlineStr"/>
-      <c r="G706" t="inlineStr"/>
-      <c r="H706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I706" t="inlineStr"/>
       <c r="J706" t="inlineStr"/>
     </row>
@@ -23804,8 +23856,16 @@
       <c r="E722" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F722" t="inlineStr"/>
-      <c r="G722" t="inlineStr"/>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H722" t="inlineStr"/>
       <c r="I722" t="inlineStr"/>
       <c r="J722" t="inlineStr"/>
@@ -23864,9 +23924,21 @@
       <c r="E724" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F724" t="inlineStr"/>
-      <c r="G724" t="inlineStr"/>
-      <c r="H724" t="inlineStr"/>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Reminded</t>
+        </is>
+      </c>
       <c r="I724" t="inlineStr"/>
       <c r="J724" t="inlineStr"/>
     </row>
@@ -24074,9 +24146,21 @@
       <c r="E731" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F731" t="inlineStr"/>
-      <c r="G731" t="inlineStr"/>
-      <c r="H731" t="inlineStr"/>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Not reachable</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not on WhatsApp </t>
+        </is>
+      </c>
       <c r="I731" t="inlineStr"/>
       <c r="J731" t="inlineStr"/>
     </row>
@@ -24104,9 +24188,21 @@
       <c r="E732" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F732" t="inlineStr"/>
-      <c r="G732" t="inlineStr"/>
-      <c r="H732" t="inlineStr"/>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Not reachable</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not on WhatsApp </t>
+        </is>
+      </c>
       <c r="I732" t="inlineStr"/>
       <c r="J732" t="inlineStr"/>
     </row>
@@ -24764,8 +24860,16 @@
       <c r="E754" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F754" t="inlineStr"/>
-      <c r="G754" t="inlineStr"/>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H754" t="inlineStr"/>
       <c r="I754" t="inlineStr"/>
       <c r="J754" t="inlineStr"/>
@@ -24794,8 +24898,16 @@
       <c r="E755" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F755" t="inlineStr"/>
-      <c r="G755" t="inlineStr"/>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr"/>
       <c r="J755" t="inlineStr"/>
@@ -24974,9 +25086,21 @@
       <c r="E761" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F761" t="inlineStr"/>
-      <c r="G761" t="inlineStr"/>
-      <c r="H761" t="inlineStr"/>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I761" t="inlineStr"/>
       <c r="J761" t="inlineStr"/>
     </row>
@@ -25154,9 +25278,21 @@
       <c r="E767" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F767" t="inlineStr"/>
-      <c r="G767" t="inlineStr"/>
-      <c r="H767" t="inlineStr"/>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>Reminded</t>
+        </is>
+      </c>
       <c r="I767" t="inlineStr"/>
       <c r="J767" t="inlineStr"/>
     </row>
@@ -25214,8 +25350,16 @@
       <c r="E769" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F769" t="inlineStr"/>
-      <c r="G769" t="inlineStr"/>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H769" t="inlineStr"/>
       <c r="I769" t="inlineStr"/>
       <c r="J769" t="inlineStr"/>
@@ -25274,9 +25418,21 @@
       <c r="E771" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F771" t="inlineStr"/>
-      <c r="G771" t="inlineStr"/>
-      <c r="H771" t="inlineStr"/>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reminded </t>
+        </is>
+      </c>
       <c r="I771" t="inlineStr"/>
       <c r="J771" t="inlineStr"/>
     </row>
@@ -25334,8 +25490,16 @@
       <c r="E773" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F773" t="inlineStr"/>
-      <c r="G773" t="inlineStr"/>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H773" t="inlineStr"/>
       <c r="I773" t="inlineStr"/>
       <c r="J773" t="inlineStr"/>
@@ -25454,9 +25618,21 @@
       <c r="E777" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F777" t="inlineStr"/>
-      <c r="G777" t="inlineStr"/>
-      <c r="H777" t="inlineStr"/>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I777" t="inlineStr"/>
       <c r="J777" t="inlineStr"/>
     </row>
@@ -25754,9 +25930,21 @@
       <c r="E787" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F787" t="inlineStr"/>
-      <c r="G787" t="inlineStr"/>
-      <c r="H787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>No Answer</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Whatsapp sent</t>
+        </is>
+      </c>
       <c r="I787" t="inlineStr"/>
       <c r="J787" t="inlineStr"/>
     </row>
@@ -25994,9 +26182,21 @@
       <c r="E795" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F795" t="inlineStr"/>
-      <c r="G795" t="inlineStr"/>
-      <c r="H795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I795" t="inlineStr"/>
       <c r="J795" t="inlineStr"/>
     </row>
@@ -26174,8 +26374,16 @@
       <c r="E801" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F801" t="inlineStr"/>
-      <c r="G801" t="inlineStr"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H801" t="inlineStr"/>
       <c r="I801" t="inlineStr"/>
       <c r="J801" t="inlineStr"/>
@@ -26444,9 +26652,21 @@
       <c r="E810" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F810" t="inlineStr"/>
-      <c r="G810" t="inlineStr"/>
-      <c r="H810" t="inlineStr"/>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Not reachable</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not on WhatsApp </t>
+        </is>
+      </c>
       <c r="I810" t="inlineStr"/>
       <c r="J810" t="inlineStr"/>
     </row>
@@ -26924,8 +27144,16 @@
       <c r="E826" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F826" t="inlineStr"/>
-      <c r="G826" t="inlineStr"/>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H826" t="inlineStr"/>
       <c r="I826" t="inlineStr"/>
       <c r="J826" t="inlineStr"/>
@@ -26954,9 +27182,21 @@
       <c r="E827" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F827" t="inlineStr"/>
-      <c r="G827" t="inlineStr"/>
-      <c r="H827" t="inlineStr"/>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I827" t="inlineStr"/>
       <c r="J827" t="inlineStr"/>
     </row>
@@ -27194,9 +27434,21 @@
       <c r="E835" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F835" t="inlineStr"/>
-      <c r="G835" t="inlineStr"/>
-      <c r="H835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Busy</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Whatsapp message sent</t>
+        </is>
+      </c>
       <c r="I835" t="inlineStr"/>
       <c r="J835" t="inlineStr"/>
     </row>
@@ -27314,9 +27566,21 @@
       <c r="E839" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F839" t="inlineStr"/>
-      <c r="G839" t="inlineStr"/>
-      <c r="H839" t="inlineStr"/>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Whatsapp message sent</t>
+        </is>
+      </c>
       <c r="I839" t="inlineStr"/>
       <c r="J839" t="inlineStr"/>
     </row>
@@ -27434,8 +27698,16 @@
       <c r="E843" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F843" t="inlineStr"/>
-      <c r="G843" t="inlineStr"/>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Invalid number</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
       <c r="H843" t="inlineStr"/>
       <c r="I843" t="inlineStr"/>
       <c r="J843" t="inlineStr"/>
@@ -27734,9 +28006,21 @@
       <c r="E853" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F853" t="inlineStr"/>
-      <c r="G853" t="inlineStr"/>
-      <c r="H853" t="inlineStr"/>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>reminded</t>
+        </is>
+      </c>
       <c r="I853" t="inlineStr"/>
       <c r="J853" t="inlineStr"/>
     </row>
@@ -27974,9 +28258,21 @@
       <c r="E861" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F861" t="inlineStr"/>
-      <c r="G861" t="inlineStr"/>
-      <c r="H861" t="inlineStr"/>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Will Renew</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He will renew today </t>
+        </is>
+      </c>
       <c r="I861" t="inlineStr"/>
       <c r="J861" t="inlineStr"/>
     </row>
